--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_23_9.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_24</t>
+          <t>model_23_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9993315455010389</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7745511707495021</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9984412777806928</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884595151091715</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9972415884540476</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00446995831250332</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.507577359294485</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007564399745899361</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02028731121205688</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01392580861435123</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08140487154507348</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06685774683986381</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000373090883141</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06970401953745223</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P2" t="n">
-        <v>144.8207523929241</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q2" t="n">
-        <v>226.4854326590935</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9993356455871942</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7745437174120178</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984351103341675</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9885854342054231</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9972605454005018</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00444254101750294</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.507627199796562</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007594330050574716</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0200659548377482</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01383010469061256</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08203534785892469</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06665238943581048</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000370802462961</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06948991964355991</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P3" t="n">
-        <v>144.833057530001</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q3" t="n">
-        <v>226.4977377961704</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9993400904713282</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7745352499305859</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9984280925714279</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9887245765962291</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9972813902129152</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004412818056832076</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.507683821883887</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007628386896641787</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01982135289842121</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0137248698975315</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08274076424222324</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06642904528014892</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000368321597398</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0692570672648057</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P4" t="n">
-        <v>144.8464835569039</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q4" t="n">
-        <v>226.5111638230734</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.999344883800671</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7745256870704783</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9984200708351201</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9888780801631651</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973042572622296</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004380765041445786</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.507747768773458</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007667315975433272</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01955150508318201</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01360942586497018</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0835252252801208</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06618734804663037</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000365646250788</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06900508047967402</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P5" t="n">
-        <v>144.8610638056991</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q5" t="n">
-        <v>226.5257440718685</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9993500396750318</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7745148074213043</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9984109211623351</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9890473941058873</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9973293452248916</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004346287685854668</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.507820521037581</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007711718872647284</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01925386380718368</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01348276957719926</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08439522570943225</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06592638080354986</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000362768553471</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0687330033207789</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P6" t="n">
-        <v>144.8768664075801</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q6" t="n">
-        <v>226.5415466737495</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.999355564945431</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7745024559155829</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9984004812366447</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9892340777898405</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9973568309215112</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00430934017725368</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.507903115613214</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007762383301666191</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01892568782234421</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01334400835742471</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0853574010994055</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06564556479499342</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00035968468162</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06844023239336894</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P7" t="n">
-        <v>144.8939409554211</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q7" t="n">
-        <v>226.5586212215906</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9993614485905397</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7744883743264922</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9983884863782531</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9894398050929021</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9973868770982092</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004269996215319955</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.507997279264303</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007820593740091704</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01856403457627114</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0131923205837483</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08642924505762492</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06534520805169998</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000356400786676</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06812708884168932</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P8" t="n">
-        <v>144.9122846761678</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q8" t="n">
-        <v>226.5769649423373</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9993676643631954</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7744723467771439</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9983747341754085</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9896659552000068</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9974196451925186</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004228431314950397</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.508104455560595</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007887332481873364</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01816647956477239</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01302689124066154</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08761613856101155</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06502638937347203</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000352931518216</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06779469739228357</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P9" t="n">
-        <v>144.9318484044687</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q9" t="n">
-        <v>226.5965286706382</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9993741714740357</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7744539923319775</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9983588610796257</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9899143691179367</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9974552613572668</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004184918234798525</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.508227191819937</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I10" t="n">
-        <v>0.007964363809340312</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0177297864353134</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01284708344708273</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08893422602105559</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06469094399371927</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000349299642399</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06744497140824708</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P10" t="n">
-        <v>144.9525362258282</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q10" t="n">
-        <v>226.6172164919977</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9993809334964131</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C11" t="n">
-        <v>0.774432940933664</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9983405948868136</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9901871850982599</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9974939812311696</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004139700560024454</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.508367962617393</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008053008715119632</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01725019630120766</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01265160661392687</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09039552694697761</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06434050481636318</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000345525490374</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06707961330960183</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P11" t="n">
-        <v>144.9742636445145</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q11" t="n">
-        <v>226.6389439106839</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9993878370779485</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C12" t="n">
-        <v>0.774408787593838</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9983194123937852</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9904858418926344</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9975357976016116</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004093536278508926</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.508529476112025</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008155806277697668</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01672517994440895</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01244049715400011</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0920209407265971</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06398074928061508</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000341672328587</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06670454223590029</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P12" t="n">
-        <v>144.99669213344</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q12" t="n">
-        <v>226.6613723996094</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9993947721866314</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7743809699997357</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D13" t="n">
-        <v>0.998294853095717</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9908124027231732</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9975808527225131</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004047161174813635</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.508715492491875</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I13" t="n">
-        <v>0.008274991303590027</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01615111037441437</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01221303690003931</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09381959529063467</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06361730247985713</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000337801570252</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06632562275239549</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P13" t="n">
-        <v>145.0194791762612</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q13" t="n">
-        <v>226.6841594424306</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9994015618315393</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C14" t="n">
-        <v>0.774348818858681</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9982662456261895</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9911687299927718</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9976291483485906</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004001758788051079</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.50893048732015</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008413821899923445</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01552471362591762</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0119692169933785</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09581579577611928</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06325945611567554</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000334012001001</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06595254212764659</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P14" t="n">
-        <v>145.0420426349758</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q14" t="n">
-        <v>226.7067229011452</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999407980489551</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7743116092225504</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D15" t="n">
-        <v>0.998232891181689</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9915565174821626</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9976806212820536</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003958837192371465</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.509179308328291</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008575689324650594</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01484301215879255</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01170935648732925</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09802980240664691</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06291929109876768</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000330429494204</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06559789558173031</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P15" t="n">
-        <v>145.0636098702519</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q15" t="n">
-        <v>226.7282901364213</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9994137214219767</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7742684263994749</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9981938981465484</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E16" t="n">
-        <v>0.991977347218796</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9977351544024526</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003920447550806352</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.509468072065035</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00876492054330894</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01410322488684223</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01143404666311674</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1004831485907988</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06261347738950737</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N16" t="n">
-        <v>1.00032722525285</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06527906274974514</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P16" t="n">
-        <v>145.0830989211454</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q16" t="n">
-        <v>226.7477791873149</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9994183871407681</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7742181494014546</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9981481829154681</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9924325697281222</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9977924413047647</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00388924786776442</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.509804274582301</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I17" t="n">
-        <v>0.008986774237368957</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01330297768711032</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01114483440293832</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1031990568613855</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06236383461401664</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000324621130734</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06501879216446999</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P17" t="n">
-        <v>145.0990789804709</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q17" t="n">
-        <v>226.7637592466403</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9994214394767625</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7741594281029895</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9980944230504532</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E18" t="n">
-        <v>0.992922934744171</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9978519754151617</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003868836882914922</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.510196944175523</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00924766813124046</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01244095258312246</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01084427713887458</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.106210624942156</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06219997494304095</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000322917501342</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06484795664806459</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P18" t="n">
-        <v>145.1096027283284</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q18" t="n">
-        <v>226.7742829944978</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9994222228194958</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7740906893611395</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9980310902713334</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E19" t="n">
-        <v>0.993448872833846</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9979130962857401</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003863598666451191</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.510656600458788</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I19" t="n">
-        <v>0.009555018890950314</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01151639267039367</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0105357091344856</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1095450339036606</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06215785281403462</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000322480286793</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06480404129282162</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P19" t="n">
-        <v>145.1123124656325</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q19" t="n">
-        <v>226.7769927318019</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9994198550133453</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7740099895790034</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9979562690976523</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9940097291297659</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9979747827570506</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003879432197082111</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.51119624027352</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009918122245845951</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01053044915690997</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01022428570137796</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.113232153222222</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M20" t="n">
-        <v>0.06228508807958861</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000323801853017</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06493669322704355</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P20" t="n">
-        <v>145.1041329540281</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q20" t="n">
-        <v>226.7688132201975</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9994132306308349</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7739149278905781</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9978676514303255</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9946037292825198</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9980356079840764</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G21" t="n">
-        <v>0.00392372947343197</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.511831918221738</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01034817928353101</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.009486241216522273</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K21" t="n">
-        <v>0.009917210250026643</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1173121714056732</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M21" t="n">
-        <v>0.06263967970409787</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N21" t="n">
-        <v>1.00032749918279</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O21" t="n">
-        <v>0.06530638055111401</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P21" t="n">
-        <v>145.0814253623734</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q21" t="n">
-        <v>226.7461056285428</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9994009399794852</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7738027118106662</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9977624921251376</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9952276690000256</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9980936953413058</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G22" t="n">
-        <v>0.004005917115600518</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.512582307664817</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01085851204942725</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.008389401755585897</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K22" t="n">
-        <v>0.009623956902506572</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1218274643443203</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M22" t="n">
-        <v>0.06329231482257951</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000334359081217</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06598679969773037</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P22" t="n">
-        <v>145.0399654640347</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q22" t="n">
-        <v>226.7046457302041</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9993812048656913</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7736697643691244</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9976374588491779</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9958763402170723</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9981465364509385</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004137885912411796</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.513471327818574</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01146529218586428</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.007249086164081675</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K23" t="n">
-        <v>0.009357189174972979</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1268160530073051</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M23" t="n">
-        <v>0.06432640136376196</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000345374028451</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06706490944382519</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P23" t="n">
-        <v>144.975140541493</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q23" t="n">
-        <v>226.6398208076624</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.99935177447111</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7735119312767975</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9974885283784908</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9965417943048107</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9981908052510604</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004334687096491419</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.514526758433719</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01218804419431556</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.006079267538348252</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009133698652324511</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1323242846532543</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06583834062680666</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000361800295194</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06864121509144344</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P24" t="n">
-        <v>144.8822117041899</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q24" t="n">
-        <v>226.5468919703593</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9993098143027509</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7733239707391368</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9973107534865769</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9972127896199331</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9982221921454389</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004615274935517404</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.515783651414534</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01305077671365954</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004899707848396386</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K25" t="n">
-        <v>0.008975242281027964</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1384024126143134</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0679358148219141</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000385219924046</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O25" t="n">
-        <v>0.07082798310540676</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P25" t="n">
-        <v>144.7567676769503</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q25" t="n">
-        <v>226.4214479431198</v>
+        <v>211.081772065143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_0</t>
+          <t>model_23_9_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9992517668494691</v>
+        <v>0.9999573537998454</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7730995443724014</v>
+        <v>0.7110100200472076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9970982242860345</v>
+        <v>0.9997561251577567</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9978737493734591</v>
+        <v>0.9997984492097056</v>
       </c>
       <c r="F26" t="n">
-        <v>0.998235117528105</v>
+        <v>0.9997920816223266</v>
       </c>
       <c r="G26" t="n">
-        <v>0.005003438522896957</v>
+        <v>2.531662663170669e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.517284391562283</v>
+        <v>0.1715569358170947</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01408217012723032</v>
+        <v>5.19195937598754e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.003737789926812115</v>
+        <v>0.0001063093201132382</v>
       </c>
       <c r="K26" t="n">
-        <v>0.008909988636937396</v>
+        <v>7.911444859686295e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1451073581368066</v>
+        <v>0.001164695737830293</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07073498796845135</v>
+        <v>0.005031563040617368</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000417618502622</v>
+        <v>1.000029243108677</v>
       </c>
       <c r="O26" t="n">
-        <v>0.07374632284787933</v>
+        <v>0.00524576709602782</v>
       </c>
       <c r="P26" t="n">
-        <v>144.5952597966582</v>
+        <v>139.1680983979192</v>
       </c>
       <c r="Q26" t="n">
-        <v>226.2599400628276</v>
+        <v>211.081772065143</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_23_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9999988643886509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.99999999999929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999998236250807</v>
       </c>
       <c r="G2" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I2" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>2.948535195063845e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.852106052195969e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>1.474270319282783e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P2" t="n">
-        <v>139.1680983979192</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q2" t="n">
-        <v>211.081772065143</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999441604761281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6592540353682896</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998765776836601</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999670673945183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.999964592377926</v>
       </c>
       <c r="G3" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>3.31487535121617e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2022815240646252</v>
       </c>
       <c r="I3" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>3.2045738525452e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001063093201132382</v>
+        <v>2.714681163454087e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>2.959627507999644e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003077072415503034</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005757495420073011</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000038289959226</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.006002603919764077</v>
       </c>
       <c r="P3" t="n">
-        <v>139.1680983979192</v>
+        <v>138.6290108869649</v>
       </c>
       <c r="Q3" t="n">
-        <v>211.081772065143</v>
+        <v>210.5426845541887</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999489908568202</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6588583152549172</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998590138672087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999602882657755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999585215971278</v>
       </c>
       <c r="G4" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>3.028123087177122e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2025164406181419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>3.66060602420128e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001063093201132382</v>
+        <v>3.273494316362075e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>3.467067680274921e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003044597495864655</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005502838437731134</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034977698181</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00573710566247128</v>
       </c>
       <c r="P4" t="n">
-        <v>139.1680983979192</v>
+        <v>138.809964961118</v>
       </c>
       <c r="Q4" t="n">
-        <v>211.081772065143</v>
+        <v>210.7236386283419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999524525849939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6584960027626989</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998422701720748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999535489190405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999525982262941</v>
       </c>
       <c r="G5" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.822619948904225e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2027315249646074</v>
       </c>
       <c r="I5" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.095344321231829e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001063093201132382</v>
+        <v>3.829028182202911e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>3.96218625171737e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.003015413960899755</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005312833470855476</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032603941718</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005539011790791222</v>
       </c>
       <c r="P5" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9505199028682</v>
       </c>
       <c r="Q5" t="n">
-        <v>211.081772065143</v>
+        <v>210.8641935700921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999548493081938</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6581649787620412</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9998264400071288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999469633355379</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.999946892347059</v>
       </c>
       <c r="G6" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.680340106451064e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2029280351108901</v>
       </c>
       <c r="I6" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.506363447849684e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001063093201132382</v>
+        <v>4.371887127726141e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>4.439125287787912e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002989099998579601</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00517720011825993</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030960474381</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005397604245575938</v>
       </c>
       <c r="P6" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0539635462142</v>
       </c>
       <c r="Q6" t="n">
-        <v>211.081772065143</v>
+        <v>210.967637213438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999564235404542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6578630938526802</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.999811573634766</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999406053649409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999414488810088</v>
       </c>
       <c r="G7" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.586886879139034e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2031072470338359</v>
       </c>
       <c r="I7" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>4.892358376231069e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001063093201132382</v>
+        <v>4.895983620092202e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>4.89412991440344e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002965509983007323</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005086144786711281</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029881000831</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005302672500052741</v>
       </c>
       <c r="P7" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1249405787582</v>
       </c>
       <c r="Q7" t="n">
-        <v>211.081772065143</v>
+        <v>211.038614245982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999573694759298</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6575882537018203</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997977206689975</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999345357758512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999363040370594</v>
       </c>
       <c r="G8" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.530732063077045e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2032704040198626</v>
       </c>
       <c r="I8" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.252040913380387e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.396308417680055e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>5.324173526066703e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002944242317521045</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005030638193188857</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029232359362</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005244802875929579</v>
       </c>
       <c r="P8" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1688337021808</v>
       </c>
       <c r="Q8" t="n">
-        <v>211.081772065143</v>
+        <v>211.0825073694047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999578388593345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6573383597234325</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997848798263832</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999287947181041</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999314788468134</v>
       </c>
       <c r="G9" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.502867436549565e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2034187518802915</v>
       </c>
       <c r="I9" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.585444382920623e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001063093201132382</v>
+        <v>5.869551912884721e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>5.727498147902672e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002925039590020647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005002866614801523</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028910496456</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005215849003955203</v>
       </c>
       <c r="P9" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1909768314982</v>
       </c>
       <c r="Q9" t="n">
-        <v>211.081772065143</v>
+        <v>211.104650498722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999579504013776</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.657111490125773</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997730124178208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999233907703243</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999269710807578</v>
       </c>
       <c r="G10" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.49624581903465e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2035534314737185</v>
       </c>
       <c r="I10" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>5.893573320249051e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001063093201132382</v>
+        <v>6.315006957564448e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.104290138906749e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002908987712433881</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.004996244408587965</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028834010484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005208944876713278</v>
       </c>
       <c r="P10" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1962750682445</v>
       </c>
       <c r="Q10" t="n">
-        <v>211.081772065143</v>
+        <v>211.1099487354683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999577993754926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6569056268061024</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997620615581381</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999183461353892</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999227825595302</v>
       </c>
       <c r="G11" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.505211367969165e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2036756408331073</v>
       </c>
       <c r="I11" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.17790470895476e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001063093201132382</v>
+        <v>6.730843337177999e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.454397316877493e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002896336888318149</v>
       </c>
       <c r="M11" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005005208654960515</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000028937571091</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005218290749612456</v>
       </c>
       <c r="P11" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1891047111245</v>
       </c>
       <c r="Q11" t="n">
-        <v>211.081772065143</v>
+        <v>211.1027783783483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999574602485194</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6567191304867706</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997520317260333</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999136481452754</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999189085683359</v>
       </c>
       <c r="G12" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.525343410049747e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2037863531044841</v>
       </c>
       <c r="I12" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.438322262776579e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.118105294792616e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>6.778213778784599e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002884993109813718</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005025279504713889</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029170115301</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005239216056992217</v>
       </c>
       <c r="P12" t="n">
-        <v>139.1680983979192</v>
+        <v>139.173096815021</v>
       </c>
       <c r="Q12" t="n">
-        <v>211.081772065143</v>
+        <v>211.0867704822448</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999569881190329</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.656550329719074</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997428326318448</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999092924549358</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999153318151308</v>
       </c>
       <c r="G13" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.553371055858057e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2038865605320023</v>
       </c>
       <c r="I13" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.677170289436653e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.477150998767171e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.077184919883085e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002874787285823527</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005053089209442137</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029493861235</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005268209678424772</v>
       </c>
       <c r="P13" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1510219923204</v>
       </c>
       <c r="Q13" t="n">
-        <v>211.081772065143</v>
+        <v>211.0646956595443</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999564313820629</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6563975857094264</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997344342847349</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999052770677022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999120475119453</v>
       </c>
       <c r="G14" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.586421367377806e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2039772359743268</v>
       </c>
       <c r="I14" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>6.895227479994597e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001063093201132382</v>
+        <v>7.808145037270449e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.35171095363391e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002865582726815837</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005085687138802196</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000029875623728</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005302195369124705</v>
       </c>
       <c r="P14" t="n">
-        <v>139.1680983979192</v>
+        <v>139.1253005122787</v>
       </c>
       <c r="Q14" t="n">
-        <v>211.081772065143</v>
+        <v>211.0389741795026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999558224423445</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6562594004592599</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997267744027386</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9999015789254174</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999090349309393</v>
       </c>
       <c r="G15" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.62257065954381e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2040592687081176</v>
       </c>
       <c r="I15" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.094110941970843e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.112988126769464e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.6035244642022e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002857267433370042</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00512110404067698</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030293182392</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005339120041835393</v>
       </c>
       <c r="P15" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0975409209258</v>
       </c>
       <c r="Q15" t="n">
-        <v>211.081772065143</v>
+        <v>211.0112145881496</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999551850897118</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6561345570328597</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997197885126676</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998981839940908</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999062756429841</v>
       </c>
       <c r="G16" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.660406665036201e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.204133381158984</v>
       </c>
       <c r="I16" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.275494676469911e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.392837108914815e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>7.834165892692363e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002849858334534094</v>
       </c>
       <c r="M16" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005157913013066623</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000030730224198</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00537749604838474</v>
       </c>
       <c r="P16" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0688929445385</v>
       </c>
       <c r="Q16" t="n">
-        <v>211.081772065143</v>
+        <v>210.9825666117624</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999545410618689</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.656021801348977</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997134465012537</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998950723727078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999037563534308</v>
       </c>
       <c r="G17" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.698638939851923e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2042003178037287</v>
       </c>
       <c r="I17" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.440160553373559e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.649332452444941e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.04474650290925e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002843172005694271</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005194842576875571</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000029243108677</v>
+        <v>1.00003117184329</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00541599778017977</v>
       </c>
       <c r="P17" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0403558308207</v>
       </c>
       <c r="Q17" t="n">
-        <v>211.081772065143</v>
+        <v>210.9540294980446</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999953903042166</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6559200128282796</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997076807830334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998922277153716</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9999014585163156</v>
       </c>
       <c r="G18" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.73651454551244e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2042607438666498</v>
       </c>
       <c r="I18" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.58986338182457e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001063093201132382</v>
+        <v>8.883821572705157e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.236816501865465e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002837177965204509</v>
       </c>
       <c r="M18" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005231170562610667</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000031609342515</v>
       </c>
       <c r="O18" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005453872323476907</v>
       </c>
       <c r="P18" t="n">
-        <v>139.1680983979192</v>
+        <v>139.0124808360233</v>
       </c>
       <c r="Q18" t="n">
-        <v>211.081772065143</v>
+        <v>210.9261545032471</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999532831934517</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6558280397839892</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9997024497253597</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998896334979113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998993668527293</v>
       </c>
       <c r="G19" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.773311442806927e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2043153430387692</v>
       </c>
       <c r="I19" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.725684124290604e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.097666580421388e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.411653012340263e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002831681723756457</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005266223924983562</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032034381633</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005490417980056479</v>
       </c>
       <c r="P19" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9857667841101</v>
       </c>
       <c r="Q19" t="n">
-        <v>211.081772065143</v>
+        <v>210.8994404513339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999526877467191</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6557450022429001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996977025165339</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998872741055218</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998974659020201</v>
       </c>
       <c r="G20" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.808659733050748e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2043646377101948</v>
       </c>
       <c r="I20" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.848942070884348e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.292154626022152e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.57054834845325e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002826815997586843</v>
       </c>
       <c r="M20" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005299678983722267</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032442687964</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00552529728990721</v>
       </c>
       <c r="P20" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9604361174698</v>
       </c>
       <c r="Q20" t="n">
-        <v>211.081772065143</v>
+        <v>210.8741097846936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999521201544347</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6556702482212634</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996934077231661</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998851212707809</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998957370680583</v>
       </c>
       <c r="G21" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.842354462920788e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044090149266439</v>
       </c>
       <c r="I21" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>7.960453367518505e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.469615833048101e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.715056910456242e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002822443661869274</v>
       </c>
       <c r="M21" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005331373615608634</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000032831894102</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005558341227889912</v>
       </c>
       <c r="P21" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9365854400363</v>
       </c>
       <c r="Q21" t="n">
-        <v>211.081772065143</v>
+        <v>210.8502591072601</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999951584177343</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6556029192434304</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996895131336427</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998831642876383</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998941671214193</v>
       </c>
       <c r="G22" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.874172378386074e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044489843163459</v>
       </c>
       <c r="I22" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.061573652107313e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.630932716314211e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.846284510243989e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002818481575305108</v>
       </c>
       <c r="M22" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005361130830698011</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033199421251</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005589365269231572</v>
       </c>
       <c r="P22" t="n">
-        <v>139.1680983979192</v>
+        <v>138.9143214011008</v>
       </c>
       <c r="Q22" t="n">
-        <v>211.081772065143</v>
+        <v>210.8279950683247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.999951081852235</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6555420430374795</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996859811279851</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998813908416274</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998927444707482</v>
       </c>
       <c r="G23" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.903992566723942e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2044851230619135</v>
       </c>
       <c r="I23" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.153279701005681e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.777120374714716e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>8.965200037860199e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002814954709530675</v>
       </c>
       <c r="M23" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005388870537249844</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033543872753</v>
       </c>
       <c r="O23" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005618285912520424</v>
       </c>
       <c r="P23" t="n">
-        <v>139.1680983979192</v>
+        <v>138.893677855358</v>
       </c>
       <c r="Q23" t="n">
-        <v>211.081772065143</v>
+        <v>210.8073515225819</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999506158737842</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6554871136610572</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996828207103892</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998797834908218</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998914610567414</v>
       </c>
       <c r="G24" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.931655060484878e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045177315125834</v>
       </c>
       <c r="I24" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.235337726583469e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0001063093201132382</v>
+        <v>9.909616570848121e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.072477148715795e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.00281176365377592</v>
       </c>
       <c r="M24" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.00541447602311145</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000033863400834</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005644981476925821</v>
       </c>
       <c r="P24" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8747166687178</v>
       </c>
       <c r="Q24" t="n">
-        <v>211.081772065143</v>
+        <v>210.7883903359416</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999501817841242</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6554376282626071</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996799391885024</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998783271890523</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998902954388404</v>
       </c>
       <c r="G25" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.957424497872321e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045471081827612</v>
       </c>
       <c r="I25" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.310154420740274e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0001063093201132382</v>
+        <v>0.0001002966158168445</v>
       </c>
       <c r="K25" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.169908001212363e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002808792176173415</v>
       </c>
       <c r="M25" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005438220754872241</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034161062315</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.00566973707107604</v>
       </c>
       <c r="P25" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8572133549259</v>
       </c>
       <c r="Q25" t="n">
-        <v>211.081772065143</v>
+        <v>210.7708870221497</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999573537998454</v>
+        <v>0.9999497789158546</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7110100200472076</v>
+        <v>0.6553931485939557</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9997561251577567</v>
+        <v>0.9996773343824424</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9997984492097056</v>
+        <v>0.9998770022629626</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9997920816223266</v>
+        <v>0.9998892375778307</v>
       </c>
       <c r="G26" t="n">
-        <v>2.531662663170669e-05</v>
+        <v>2.981340498659082e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1715569358170947</v>
+        <v>0.2045735132354943</v>
       </c>
       <c r="I26" t="n">
-        <v>5.19195937598754e-05</v>
+        <v>8.377786382595859e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001063093201132382</v>
+        <v>0.0001013887710976616</v>
       </c>
       <c r="K26" t="n">
-        <v>7.911444859686295e-05</v>
+        <v>9.258331746181007e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.001164695737830293</v>
+        <v>0.002806305810341406</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005031563040617368</v>
+        <v>0.005460165289310464</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000029243108677</v>
+        <v>1.000034437314843</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00524576709602782</v>
+        <v>0.005692615829776747</v>
       </c>
       <c r="P26" t="n">
-        <v>139.1680983979192</v>
+        <v>138.8411048676642</v>
       </c>
       <c r="Q26" t="n">
-        <v>211.081772065143</v>
+        <v>210.754778534888</v>
       </c>
     </row>
   </sheetData>
